--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_jh_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_jh_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>24-02-2021 08:30</t>
+          <t>2021-02-24 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>28-05-2021 08:30</t>
+          <t>2021-05-28 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>21-07-2021 08:30</t>
+          <t>2021-07-21 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>21-08-2021 08:30</t>
+          <t>2021-08-21 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>16-09-2021 08:30</t>
+          <t>2021-09-16 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>27-11-2021 08:30</t>
+          <t>2021-11-27 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>23-12-2021 08:30</t>
+          <t>2021-12-23 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>25-07-2021 08:30</t>
+          <t>2021-07-25 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>25-07-2021 08:30</t>
+          <t>2021-07-25 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>25-07-2021 08:30</t>
+          <t>2021-07-25 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>23-08-2021 08:30</t>
+          <t>2021-08-23 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>18-09-2021 08:30</t>
+          <t>2021-09-18 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>19-03-2021 08:30</t>
+          <t>2021-03-19 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7415,7 +7415,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7508,7 +7508,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -9926,7 +9926,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -10947,7 +10947,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -11780,7 +11780,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -11873,7 +11873,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12059,7 +12059,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12152,7 +12152,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12245,7 +12245,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12431,7 +12431,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12524,7 +12524,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12617,7 +12617,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
